--- a/Datos Tesis Upstream/Algoritmos y Programacion/2526-3/Asistencia y participacion Algoritmos 2526-3.xlsx
+++ b/Datos Tesis Upstream/Algoritmos y Programacion/2526-3/Asistencia y participacion Algoritmos 2526-3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nelsoncarrillo/Downloads/tesis-prediccion-participacion/Datos Tesis Upstream/Algoritmos y Programacion/2526-3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E21A0FA-CD49-E341-A62D-5471A57EBE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611A5D81-6184-3744-8959-0531414272B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sec 1" sheetId="1" r:id="rId1"/>
@@ -48,6 +48,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica</t>
@@ -74,6 +75,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -87,6 +89,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -100,6 +103,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -113,6 +117,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Sospecha de fraude académico en la dinámica de evaluación continua</t>
@@ -126,6 +131,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -139,6 +145,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -152,6 +159,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Dinámica
@@ -166,6 +174,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Dinámica
@@ -180,6 +189,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -193,6 +203,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -206,6 +217,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dudosa</t>
@@ -219,6 +231,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Fraude académico: usó el resumen de IA de Bing Search 4 veces durante la clase. No se le permitió completar la dinámica de diccionarios</t>
@@ -232,6 +245,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>una intervención normal (+1), una intervención "buena pregunta" (+1,5), una repregunta (+0,5)</t>
@@ -245,6 +259,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -258,6 +273,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -271,6 +287,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Dinámica
@@ -285,6 +302,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -298,6 +316,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -311,6 +330,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>1 intervencion + 1 RETROACTIVO corrección fecha parcial</t>
@@ -324,7 +344,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
-            <scheme val="minor"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Dinámica (pero no estuvo la clase siguiente para recoger su galleta)
 </t>
@@ -352,6 +372,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -365,6 +386,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>RETROACTIVO corrección fecha parcial</t>
@@ -378,6 +400,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -391,6 +414,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica + intervención</t>
@@ -404,6 +428,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -417,6 +442,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó tarde: no realizó dinámica 2 de clase 2</t>
@@ -430,6 +456,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Sospecha de fraude académico en la dinámica de evaluación continua</t>
@@ -443,6 +470,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica</t>
@@ -456,6 +484,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -469,6 +498,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica</t>
@@ -482,6 +512,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica</t>
@@ -495,6 +526,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica</t>
@@ -508,6 +540,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica+Proyecto</t>
@@ -521,6 +554,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámicas anuladas por no realizarse en el salón</t>
@@ -534,6 +568,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -547,6 +582,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Intervención + Dinámica</t>
@@ -560,6 +596,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica</t>
@@ -573,6 +610,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica (+2), una intervención de aporte (+1), y una intervención de repregunta (+0.5)</t>
@@ -586,6 +624,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó a las 7:40, después de la dinámica 2 de listas</t>
@@ -599,6 +638,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -612,6 +652,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -625,6 +666,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica</t>
@@ -638,6 +680,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica + intervención</t>
@@ -651,6 +694,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -667,20 +711,21 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="T7" authorId="0" shapeId="0" xr:uid="{966700D5-EE2E-0841-8EB0-0B4D2F5AF84E}">
+    <comment ref="U7" authorId="0" shapeId="0" xr:uid="{966700D5-EE2E-0841-8EB0-0B4D2F5AF84E}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica</t>
         </r>
       </text>
     </comment>
-    <comment ref="U7" authorId="0" shapeId="0" xr:uid="{C91F8385-4B8F-4644-93E5-18CB5C87E4B8}">
+    <comment ref="V7" authorId="0" shapeId="0" xr:uid="{C91F8385-4B8F-4644-93E5-18CB5C87E4B8}">
       <text>
         <r>
           <rPr>
@@ -693,91 +738,98 @@
         </r>
       </text>
     </comment>
-    <comment ref="U10" authorId="0" shapeId="0" xr:uid="{58D53BD3-3885-2A40-8670-30D9372857C1}">
+    <comment ref="V10" authorId="0" shapeId="0" xr:uid="{58D53BD3-3885-2A40-8670-30D9372857C1}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="U11" authorId="0" shapeId="0" xr:uid="{31F6B4D0-FC28-B64C-A574-8384B1AE6A3C}">
+    <comment ref="V11" authorId="0" shapeId="0" xr:uid="{31F6B4D0-FC28-B64C-A574-8384B1AE6A3C}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="U12" authorId="0" shapeId="0" xr:uid="{18E0577E-DD21-D042-B5E0-B2B7A6C12335}">
+    <comment ref="V12" authorId="0" shapeId="0" xr:uid="{18E0577E-DD21-D042-B5E0-B2B7A6C12335}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{861ED058-E4C4-134E-9F19-37EE4E2A04B1}">
+    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{861ED058-E4C4-134E-9F19-37EE4E2A04B1}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Sospecha de fraude académico en la dinámica de evaluación continua</t>
         </r>
       </text>
     </comment>
-    <comment ref="U13" authorId="0" shapeId="0" xr:uid="{7C63F582-1798-3344-AEF1-6EB7E6A6AF19}">
+    <comment ref="V13" authorId="0" shapeId="0" xr:uid="{7C63F582-1798-3344-AEF1-6EB7E6A6AF19}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="U15" authorId="0" shapeId="0" xr:uid="{5ECC68C4-A3B0-F34A-AA30-2C0D71F86D24}">
+    <comment ref="V15" authorId="0" shapeId="0" xr:uid="{5ECC68C4-A3B0-F34A-AA30-2C0D71F86D24}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{BD23AD23-7299-7547-B70E-64852E03E98F}">
+    <comment ref="J16" authorId="0" shapeId="0" xr:uid="{BD23AD23-7299-7547-B70E-64852E03E98F}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Dinámica
@@ -785,13 +837,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="M16" authorId="0" shapeId="0" xr:uid="{E05540B7-D3D5-D446-AE85-DC952D591693}">
+    <comment ref="N16" authorId="0" shapeId="0" xr:uid="{E05540B7-D3D5-D446-AE85-DC952D591693}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Dinámica
@@ -799,104 +852,112 @@
         </r>
       </text>
     </comment>
-    <comment ref="U16" authorId="0" shapeId="0" xr:uid="{BFE6CC2E-B3CA-1743-B9AC-007673CD7135}">
+    <comment ref="V16" authorId="0" shapeId="0" xr:uid="{BFE6CC2E-B3CA-1743-B9AC-007673CD7135}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="U17" authorId="0" shapeId="0" xr:uid="{1032B928-E462-C942-89F0-5675668CC039}">
+    <comment ref="V17" authorId="0" shapeId="0" xr:uid="{1032B928-E462-C942-89F0-5675668CC039}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{0D4F91C1-2B11-A54C-87AC-EA2B17BBFC60}">
+    <comment ref="F19" authorId="0" shapeId="0" xr:uid="{0D4F91C1-2B11-A54C-87AC-EA2B17BBFC60}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dudosa</t>
         </r>
       </text>
     </comment>
-    <comment ref="K19" authorId="0" shapeId="0" xr:uid="{EF3E9469-4423-3347-9EC0-3E7AA2847872}">
+    <comment ref="L19" authorId="0" shapeId="0" xr:uid="{EF3E9469-4423-3347-9EC0-3E7AA2847872}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Fraude académico: usó el resumen de IA de Bing Search 4 veces durante la clase. No se le permitió completar la dinámica de diccionarios</t>
         </r>
       </text>
     </comment>
-    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{B7DB4A84-2F91-514F-8E11-066E30F798A8}">
+    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{B7DB4A84-2F91-514F-8E11-066E30F798A8}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>una intervención normal (+1), una intervención "buena pregunta" (+1,5), una repregunta (+0,5)</t>
         </r>
       </text>
     </comment>
-    <comment ref="U20" authorId="0" shapeId="0" xr:uid="{12B2EFE5-7FA6-B148-9E1C-F3AEAB75588B}">
+    <comment ref="V20" authorId="0" shapeId="0" xr:uid="{12B2EFE5-7FA6-B148-9E1C-F3AEAB75588B}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="U21" authorId="0" shapeId="0" xr:uid="{9487F6A3-94AB-0C4C-B5B8-4E08CC724BB9}">
+    <comment ref="V21" authorId="0" shapeId="0" xr:uid="{9487F6A3-94AB-0C4C-B5B8-4E08CC724BB9}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="K22" authorId="0" shapeId="0" xr:uid="{CB1B0538-D76A-0C42-B438-5DC94AB15A01}">
+    <comment ref="L22" authorId="0" shapeId="0" xr:uid="{CB1B0538-D76A-0C42-B438-5DC94AB15A01}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Dinámica
@@ -904,52 +965,56 @@
         </r>
       </text>
     </comment>
-    <comment ref="U22" authorId="0" shapeId="0" xr:uid="{C9299B8A-160E-994A-BC2B-D03506DA415F}">
+    <comment ref="V22" authorId="0" shapeId="0" xr:uid="{C9299B8A-160E-994A-BC2B-D03506DA415F}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="U23" authorId="0" shapeId="0" xr:uid="{BE32AF85-86C0-5F4E-85ED-09ECDFA499B6}">
+    <comment ref="V23" authorId="0" shapeId="0" xr:uid="{BE32AF85-86C0-5F4E-85ED-09ECDFA499B6}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="X23" authorId="0" shapeId="0" xr:uid="{C3EC0670-F601-E845-A111-FA15A18B40C2}">
+    <comment ref="Y23" authorId="0" shapeId="0" xr:uid="{C3EC0670-F601-E845-A111-FA15A18B40C2}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>1 intervencion + 1 RETROACTIVO corrección fecha parcial</t>
         </r>
       </text>
     </comment>
-    <comment ref="G24" authorId="0" shapeId="0" xr:uid="{E286DDDC-94C7-BC45-BB3B-8B8920A572D8}">
+    <comment ref="H24" authorId="0" shapeId="0" xr:uid="{E286DDDC-94C7-BC45-BB3B-8B8920A572D8}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Dinámica (pero no estuvo la clase siguiente para recoger su galleta)
@@ -957,7 +1022,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M24" authorId="0" shapeId="0" xr:uid="{97AA7D99-3C9D-BD4F-B5B7-A42D7C3F6036}">
+    <comment ref="N24" authorId="0" shapeId="0" xr:uid="{97AA7D99-3C9D-BD4F-B5B7-A42D7C3F6036}">
       <text>
         <r>
           <rPr>
@@ -971,312 +1036,336 @@
         </r>
       </text>
     </comment>
-    <comment ref="U24" authorId="0" shapeId="0" xr:uid="{A7DA978A-5FDC-E240-A8D2-2F21C8866BF1}">
+    <comment ref="V24" authorId="0" shapeId="0" xr:uid="{A7DA978A-5FDC-E240-A8D2-2F21C8866BF1}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="X24" authorId="0" shapeId="0" xr:uid="{30C702DC-0752-3340-960D-C958B463F190}">
+    <comment ref="Y24" authorId="0" shapeId="0" xr:uid="{30C702DC-0752-3340-960D-C958B463F190}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>RETROACTIVO corrección fecha parcial</t>
         </r>
       </text>
     </comment>
-    <comment ref="U27" authorId="0" shapeId="0" xr:uid="{7D74D6E8-91DD-9648-9CD4-B663E5F2DE82}">
+    <comment ref="V27" authorId="0" shapeId="0" xr:uid="{7D74D6E8-91DD-9648-9CD4-B663E5F2DE82}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="T29" authorId="0" shapeId="0" xr:uid="{3A77D0C8-5355-2945-953C-BE847ED4DBD3}">
+    <comment ref="U29" authorId="0" shapeId="0" xr:uid="{3A77D0C8-5355-2945-953C-BE847ED4DBD3}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica + intervención</t>
         </r>
       </text>
     </comment>
-    <comment ref="U29" authorId="0" shapeId="0" xr:uid="{6FB2B561-3901-5540-8C25-91E54A4830C7}">
+    <comment ref="V29" authorId="0" shapeId="0" xr:uid="{6FB2B561-3901-5540-8C25-91E54A4830C7}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="H31" authorId="0" shapeId="0" xr:uid="{94CBEA5A-86FA-F745-B003-B7F9C67F5C62}">
+    <comment ref="I31" authorId="0" shapeId="0" xr:uid="{94CBEA5A-86FA-F745-B003-B7F9C67F5C62}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó tarde: no realizó dinámica 2 de clase 2</t>
         </r>
       </text>
     </comment>
-    <comment ref="Q31" authorId="0" shapeId="0" xr:uid="{EE7FE426-EA20-DA4D-82EF-10816CDA74F9}">
+    <comment ref="R31" authorId="0" shapeId="0" xr:uid="{EE7FE426-EA20-DA4D-82EF-10816CDA74F9}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Sospecha de fraude académico en la dinámica de evaluación continua</t>
         </r>
       </text>
     </comment>
-    <comment ref="T31" authorId="0" shapeId="0" xr:uid="{5D256FF8-61F2-624B-9BCD-0DE9604C40C8}">
+    <comment ref="U31" authorId="0" shapeId="0" xr:uid="{5D256FF8-61F2-624B-9BCD-0DE9604C40C8}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica</t>
         </r>
       </text>
     </comment>
-    <comment ref="U31" authorId="0" shapeId="0" xr:uid="{00EB33DA-3C99-1845-AD3F-B588351F0E81}">
+    <comment ref="V31" authorId="0" shapeId="0" xr:uid="{00EB33DA-3C99-1845-AD3F-B588351F0E81}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="F32" authorId="0" shapeId="0" xr:uid="{B034DB38-1695-EF47-81C1-B8DAAB6B1417}">
+    <comment ref="G32" authorId="0" shapeId="0" xr:uid="{B034DB38-1695-EF47-81C1-B8DAAB6B1417}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica</t>
         </r>
       </text>
     </comment>
-    <comment ref="K32" authorId="0" shapeId="0" xr:uid="{A464760A-92A0-CA49-B541-0457A2AE85BF}">
+    <comment ref="L32" authorId="0" shapeId="0" xr:uid="{A464760A-92A0-CA49-B541-0457A2AE85BF}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica</t>
         </r>
       </text>
     </comment>
-    <comment ref="Q32" authorId="0" shapeId="0" xr:uid="{4A14FA99-E522-A04A-B8AF-21376A7F38E6}">
+    <comment ref="R32" authorId="0" shapeId="0" xr:uid="{4A14FA99-E522-A04A-B8AF-21376A7F38E6}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica</t>
         </r>
       </text>
     </comment>
-    <comment ref="U32" authorId="0" shapeId="0" xr:uid="{EB2DF41C-FC82-2D4A-AAC5-1CECAE99083F}">
+    <comment ref="V32" authorId="0" shapeId="0" xr:uid="{EB2DF41C-FC82-2D4A-AAC5-1CECAE99083F}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica+Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="K33" authorId="0" shapeId="0" xr:uid="{4DD7C86F-C165-5B4A-BC1C-334C6A5CA4E0}">
+    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{4DD7C86F-C165-5B4A-BC1C-334C6A5CA4E0}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámicas anuladas por no realizarse en el salón</t>
         </r>
       </text>
     </comment>
-    <comment ref="U33" authorId="0" shapeId="0" xr:uid="{5AECE6DF-0FAF-4943-9D62-0503A5DC1E66}">
+    <comment ref="V33" authorId="0" shapeId="0" xr:uid="{5AECE6DF-0FAF-4943-9D62-0503A5DC1E66}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="G34" authorId="0" shapeId="0" xr:uid="{082E3AA6-A4FE-9D4F-B847-21E99B68FB97}">
+    <comment ref="H34" authorId="0" shapeId="0" xr:uid="{082E3AA6-A4FE-9D4F-B847-21E99B68FB97}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Intervención + Dinámica</t>
         </r>
       </text>
     </comment>
-    <comment ref="H34" authorId="0" shapeId="0" xr:uid="{77A3CF25-8FD9-054A-896E-9F74C105DA9C}">
+    <comment ref="I34" authorId="0" shapeId="0" xr:uid="{77A3CF25-8FD9-054A-896E-9F74C105DA9C}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica</t>
         </r>
       </text>
     </comment>
-    <comment ref="J34" authorId="0" shapeId="0" xr:uid="{8D9ECB66-E0A1-6A4F-902F-36941C756BDB}">
+    <comment ref="K34" authorId="0" shapeId="0" xr:uid="{8D9ECB66-E0A1-6A4F-902F-36941C756BDB}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica (+2), una intervención de aporte (+1), y una intervención de repregunta (+0.5)</t>
         </r>
       </text>
     </comment>
-    <comment ref="K34" authorId="0" shapeId="0" xr:uid="{3DE7F2DD-A96B-C142-BB93-B91EB0D329E1}">
+    <comment ref="L34" authorId="0" shapeId="0" xr:uid="{3DE7F2DD-A96B-C142-BB93-B91EB0D329E1}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Llegó a las 7:40, después de la dinámica 2 de listas</t>
         </r>
       </text>
     </comment>
-    <comment ref="U34" authorId="0" shapeId="0" xr:uid="{09E8B05F-E574-ED4C-AA52-B28CA1F6AC5C}">
+    <comment ref="V34" authorId="0" shapeId="0" xr:uid="{09E8B05F-E574-ED4C-AA52-B28CA1F6AC5C}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="U35" authorId="0" shapeId="0" xr:uid="{E006EF33-C5DE-C342-BF90-E4C3EEFA8CC1}">
+    <comment ref="V35" authorId="0" shapeId="0" xr:uid="{E006EF33-C5DE-C342-BF90-E4C3EEFA8CC1}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
         </r>
       </text>
     </comment>
-    <comment ref="X35" authorId="0" shapeId="0" xr:uid="{EE7EAB1E-FB40-C54E-AD63-2A308F6D7EC5}">
+    <comment ref="Y35" authorId="0" shapeId="0" xr:uid="{EE7EAB1E-FB40-C54E-AD63-2A308F6D7EC5}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica</t>
         </r>
       </text>
     </comment>
-    <comment ref="T36" authorId="0" shapeId="0" xr:uid="{40A064B9-15CC-B84B-BB1B-0962235D9953}">
+    <comment ref="U36" authorId="0" shapeId="0" xr:uid="{40A064B9-15CC-B84B-BB1B-0962235D9953}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Dinámica + intervención</t>
         </r>
       </text>
     </comment>
-    <comment ref="U36" authorId="0" shapeId="0" xr:uid="{9A8CCA47-89D8-434B-85D3-45F3A4D93E8F}">
+    <comment ref="V36" authorId="0" shapeId="0" xr:uid="{9A8CCA47-89D8-434B-85D3-45F3A4D93E8F}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Proyecto</t>
@@ -1288,7 +1377,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="481">
   <si>
     <t>P=Presente, 1=intervención, T=Tardy, F=Fraude</t>
   </si>
@@ -2881,6 +2970,9 @@
   <si>
     <t>2526-3</t>
   </si>
+  <si>
+    <t>carnet</t>
+  </si>
 </sst>
 </file>
 
@@ -2890,7 +2982,7 @@
     <numFmt numFmtId="164" formatCode="d\ mmm"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2969,6 +3061,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -3069,7 +3169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3154,19 +3254,6 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3206,6 +3293,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3676,12 +3784,14 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.6640625" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="9.1640625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" customWidth="1"/>
     <col min="4" max="5" width="9.1640625" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="9.1640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="6.83203125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" customWidth="1"/>
+    <col min="8" max="8" width="23.83203125" customWidth="1"/>
+    <col min="9" max="9" width="24.6640625" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="12" width="6.5" customWidth="1"/>
     <col min="13" max="13" width="7.83203125" customWidth="1"/>
     <col min="14" max="15" width="6.5" customWidth="1"/>
@@ -3719,61 +3829,61 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="38" t="s">
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="40" t="s">
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="38" t="s">
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="40" t="s">
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="38" t="s">
+      <c r="X1" s="54"/>
+      <c r="Y1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="40" t="s">
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="AB1" s="39"/>
-      <c r="AC1" s="39"/>
-      <c r="AD1" s="38" t="s">
+      <c r="AB1" s="54"/>
+      <c r="AC1" s="54"/>
+      <c r="AD1" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="40" t="s">
+      <c r="AE1" s="54"/>
+      <c r="AF1" s="54"/>
+      <c r="AG1" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="AH1" s="39"/>
-      <c r="AI1" s="38" t="s">
+      <c r="AH1" s="54"/>
+      <c r="AI1" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="AJ1" s="39"/>
-      <c r="AK1" s="39"/>
-      <c r="AL1" s="38" t="s">
+      <c r="AJ1" s="54"/>
+      <c r="AK1" s="54"/>
+      <c r="AL1" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="AM1" s="39"/>
-      <c r="AN1" s="38" t="s">
+      <c r="AM1" s="54"/>
+      <c r="AN1" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="AO1" s="39"/>
+      <c r="AO1" s="54"/>
       <c r="AP1" s="2"/>
     </row>
     <row r="2" spans="1:42">
@@ -8365,57 +8475,57 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
-      <c r="K1" s="41" t="s">
+      <c r="K1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="38" t="s">
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="41" t="s">
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="38" t="s">
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="41" t="s">
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="38" t="s">
+      <c r="X1" s="54"/>
+      <c r="Y1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="41" t="s">
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="AB1" s="39"/>
-      <c r="AC1" s="39"/>
-      <c r="AD1" s="38" t="s">
+      <c r="AB1" s="54"/>
+      <c r="AC1" s="54"/>
+      <c r="AD1" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="41" t="s">
+      <c r="AE1" s="54"/>
+      <c r="AF1" s="54"/>
+      <c r="AG1" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="AH1" s="39"/>
-      <c r="AI1" s="38" t="s">
+      <c r="AH1" s="54"/>
+      <c r="AI1" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="AJ1" s="39"/>
-      <c r="AK1" s="39"/>
-      <c r="AL1" s="38" t="s">
+      <c r="AJ1" s="54"/>
+      <c r="AK1" s="54"/>
+      <c r="AL1" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="AM1" s="39"/>
+      <c r="AM1" s="54"/>
       <c r="AN1" s="2"/>
     </row>
     <row r="2" spans="1:40">
@@ -11652,57 +11762,57 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
-      <c r="K1" s="42" t="s">
+      <c r="K1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="38" t="s">
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="42" t="s">
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="38" t="s">
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="42" t="s">
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="38" t="s">
+      <c r="X1" s="54"/>
+      <c r="Y1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="42" t="s">
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="AB1" s="39"/>
-      <c r="AC1" s="39"/>
-      <c r="AD1" s="38" t="s">
+      <c r="AB1" s="54"/>
+      <c r="AC1" s="54"/>
+      <c r="AD1" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="42" t="s">
+      <c r="AE1" s="54"/>
+      <c r="AF1" s="54"/>
+      <c r="AG1" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="AH1" s="39"/>
-      <c r="AI1" s="38" t="s">
+      <c r="AH1" s="54"/>
+      <c r="AI1" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="AJ1" s="39"/>
-      <c r="AK1" s="39"/>
-      <c r="AL1" s="38" t="s">
+      <c r="AJ1" s="54"/>
+      <c r="AK1" s="54"/>
+      <c r="AL1" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="AM1" s="39"/>
+      <c r="AM1" s="54"/>
       <c r="AN1" s="2"/>
     </row>
     <row r="2" spans="1:40">
@@ -14828,2049 +14938,2204 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AB36"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22.33203125" customWidth="1"/>
-    <col min="3" max="4" width="16" customWidth="1"/>
-    <col min="5" max="28" width="9" customWidth="1"/>
+    <col min="3" max="5" width="16" customWidth="1"/>
+    <col min="6" max="29" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>457</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="50" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:29">
       <c r="A2" t="s">
         <v>458</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="50" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:29">
       <c r="A3" t="s">
         <v>459</v>
       </c>
-      <c r="B3" s="56">
+      <c r="B3" s="51">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
-      <c r="A5" s="39" t="s">
+    <row r="5" spans="1:29">
+      <c r="A5" s="54" t="s">
         <v>460</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="54" t="s">
         <v>461</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="54" t="s">
         <v>462</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="54" t="s">
         <v>463</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E5" s="60" t="s">
+        <v>480</v>
+      </c>
+      <c r="F5" s="54" t="s">
         <v>464</v>
       </c>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39" t="s">
+      <c r="G5" s="54"/>
+      <c r="H5" s="54" t="s">
         <v>465</v>
       </c>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39" t="s">
+      <c r="I5" s="54"/>
+      <c r="J5" s="54" t="s">
         <v>466</v>
       </c>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39" t="s">
+      <c r="K5" s="54"/>
+      <c r="L5" s="54" t="s">
         <v>467</v>
       </c>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39" t="s">
+      <c r="M5" s="54"/>
+      <c r="N5" s="54" t="s">
         <v>468</v>
       </c>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39" t="s">
+      <c r="O5" s="54"/>
+      <c r="P5" s="54" t="s">
         <v>469</v>
       </c>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39" t="s">
+      <c r="Q5" s="54"/>
+      <c r="R5" s="54" t="s">
         <v>470</v>
       </c>
-      <c r="R5" s="39"/>
-      <c r="S5" s="39" t="s">
+      <c r="S5" s="54"/>
+      <c r="T5" s="54" t="s">
         <v>471</v>
       </c>
-      <c r="T5" s="39"/>
-      <c r="U5" s="39" t="s">
+      <c r="U5" s="54"/>
+      <c r="V5" s="54" t="s">
         <v>472</v>
       </c>
-      <c r="V5" s="39"/>
-      <c r="W5" s="39" t="s">
+      <c r="W5" s="54"/>
+      <c r="X5" s="54" t="s">
         <v>473</v>
       </c>
-      <c r="X5" s="39"/>
-      <c r="Y5" s="39" t="s">
+      <c r="Y5" s="54"/>
+      <c r="Z5" s="54" t="s">
         <v>474</v>
       </c>
-      <c r="Z5" s="39"/>
-      <c r="AA5" s="39" t="s">
+      <c r="AA5" s="54"/>
+      <c r="AB5" s="54" t="s">
         <v>475</v>
       </c>
-      <c r="AB5" s="39"/>
+      <c r="AC5" s="54"/>
     </row>
-    <row r="6" spans="1:28">
-      <c r="A6" s="39"/>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="43" t="s">
+    <row r="6" spans="1:29">
+      <c r="A6" s="54"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="F6" s="43" t="s">
+      <c r="G6" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="H6" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="H6" s="43" t="s">
+      <c r="I6" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="I6" s="43" t="s">
+      <c r="J6" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="J6" s="43" t="s">
+      <c r="K6" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="K6" s="43" t="s">
+      <c r="L6" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="L6" s="43" t="s">
+      <c r="M6" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="M6" s="43" t="s">
+      <c r="N6" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="N6" s="43" t="s">
+      <c r="O6" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="O6" s="43" t="s">
+      <c r="P6" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="P6" s="43" t="s">
+      <c r="Q6" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="Q6" s="43" t="s">
+      <c r="R6" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="R6" s="43" t="s">
+      <c r="S6" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="S6" s="43" t="s">
+      <c r="T6" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="T6" s="43" t="s">
+      <c r="U6" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="U6" s="43" t="s">
+      <c r="V6" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="V6" s="43" t="s">
+      <c r="W6" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="W6" s="43" t="s">
+      <c r="X6" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="X6" s="43" t="s">
+      <c r="Y6" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="Y6" s="43" t="s">
+      <c r="Z6" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="Z6" s="43" t="s">
+      <c r="AA6" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="AA6" s="43" t="s">
+      <c r="AB6" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="AB6" s="43" t="s">
+      <c r="AC6" s="38" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
-      <c r="A7" s="44">
+    <row r="7" spans="1:29">
+      <c r="A7" s="39">
         <v>1</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="46">
+      <c r="D7" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="41">
         <v>1</v>
       </c>
-      <c r="F7" s="46">
+      <c r="G7" s="41">
         <v>1</v>
       </c>
-      <c r="G7" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="K7" s="46">
+      <c r="H7" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="41">
         <v>2</v>
       </c>
-      <c r="L7" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="M7" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="N7" s="46"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q7" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="R7" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="S7" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="T7" s="46">
+      <c r="M7" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="N7" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="O7" s="41"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="R7" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="S7" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="T7" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="U7" s="41">
         <v>2</v>
       </c>
-      <c r="U7" s="46">
+      <c r="V7" s="41">
         <v>2</v>
       </c>
-      <c r="V7" s="44"/>
-      <c r="W7" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="X7" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y7" s="44"/>
-      <c r="Z7" s="44"/>
-      <c r="AA7" s="44"/>
-      <c r="AB7" s="44"/>
+      <c r="W7" s="39"/>
+      <c r="X7" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y7" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z7" s="39"/>
+      <c r="AA7" s="39"/>
+      <c r="AB7" s="39"/>
+      <c r="AC7" s="39"/>
     </row>
-    <row r="8" spans="1:28">
-      <c r="A8" s="44">
+    <row r="8" spans="1:29">
+      <c r="A8" s="39">
         <v>2</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="44"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="K8" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="L8" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="M8" s="49"/>
-      <c r="N8" s="49"/>
+      <c r="D8" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="44"/>
       <c r="O8" s="44"/>
-      <c r="P8" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q8" s="49"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="49"/>
-      <c r="U8" s="49"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="R8" s="44"/>
+      <c r="S8" s="44"/>
+      <c r="T8" s="44"/>
+      <c r="U8" s="44"/>
       <c r="V8" s="44"/>
-      <c r="W8" s="49"/>
-      <c r="X8" s="49"/>
+      <c r="W8" s="39"/>
+      <c r="X8" s="44"/>
       <c r="Y8" s="44"/>
-      <c r="Z8" s="44"/>
-      <c r="AA8" s="44"/>
-      <c r="AB8" s="44"/>
+      <c r="Z8" s="39"/>
+      <c r="AA8" s="39"/>
+      <c r="AB8" s="39"/>
+      <c r="AC8" s="39"/>
     </row>
-    <row r="9" spans="1:28">
-      <c r="A9" s="44">
+    <row r="9" spans="1:29">
+      <c r="A9" s="39">
         <v>3</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="44"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
-      <c r="O9" s="44"/>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="46"/>
-      <c r="S9" s="46"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
-      <c r="V9" s="44"/>
-      <c r="W9" s="46"/>
-      <c r="X9" s="46"/>
-      <c r="Y9" s="44"/>
-      <c r="Z9" s="44"/>
-      <c r="AA9" s="44"/>
-      <c r="AB9" s="44"/>
+      <c r="D9" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="41"/>
+      <c r="T9" s="41"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="41"/>
+      <c r="W9" s="39"/>
+      <c r="X9" s="41"/>
+      <c r="Y9" s="41"/>
+      <c r="Z9" s="39"/>
+      <c r="AA9" s="39"/>
+      <c r="AB9" s="39"/>
+      <c r="AC9" s="39"/>
     </row>
-    <row r="10" spans="1:28">
-      <c r="A10" s="44">
+    <row r="10" spans="1:29">
+      <c r="A10" s="39">
         <v>4</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="50"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="L10" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="M10" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="N10" s="49"/>
+      <c r="D10" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="45"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="44" t="s">
+        <v>53</v>
+      </c>
       <c r="O10" s="44"/>
-      <c r="P10" s="49"/>
-      <c r="Q10" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="R10" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S10" s="49"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="49">
+      <c r="P10" s="39"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="S10" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="T10" s="44"/>
+      <c r="U10" s="44"/>
+      <c r="V10" s="44">
         <v>2</v>
       </c>
-      <c r="V10" s="44"/>
-      <c r="W10" s="49"/>
-      <c r="X10" s="49"/>
+      <c r="W10" s="39"/>
+      <c r="X10" s="44"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="44"/>
-      <c r="AA10" s="44"/>
-      <c r="AB10" s="44"/>
+      <c r="Z10" s="39"/>
+      <c r="AA10" s="39"/>
+      <c r="AB10" s="39"/>
+      <c r="AC10" s="39"/>
     </row>
-    <row r="11" spans="1:28">
-      <c r="A11" s="44">
+    <row r="11" spans="1:29">
+      <c r="A11" s="39">
         <v>5</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46">
+      <c r="D11" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41">
         <v>1</v>
       </c>
-      <c r="G11" s="46">
+      <c r="H11" s="41">
         <v>1</v>
       </c>
-      <c r="H11" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="I11" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="J11" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="K11" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="L11" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="M11" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="N11" s="46"/>
-      <c r="O11" s="44"/>
-      <c r="P11" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q11" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="R11" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="S11" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="T11" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="U11" s="46">
+      <c r="I11" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="M11" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="O11" s="41"/>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="R11" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="S11" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="T11" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="U11" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="V11" s="41">
         <v>2</v>
       </c>
-      <c r="V11" s="44"/>
-      <c r="W11" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="X11" s="46">
+      <c r="W11" s="39"/>
+      <c r="X11" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y11" s="41">
         <v>1</v>
       </c>
-      <c r="Y11" s="44"/>
-      <c r="Z11" s="44"/>
-      <c r="AA11" s="44"/>
-      <c r="AB11" s="44"/>
+      <c r="Z11" s="39"/>
+      <c r="AA11" s="39"/>
+      <c r="AB11" s="39"/>
+      <c r="AC11" s="39"/>
     </row>
-    <row r="12" spans="1:28">
-      <c r="A12" s="44">
+    <row r="12" spans="1:29">
+      <c r="A12" s="39">
         <v>6</v>
       </c>
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="49">
+      <c r="D12" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="44">
         <v>1</v>
       </c>
-      <c r="H12" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="J12" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="K12" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="L12" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="M12" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="N12" s="49"/>
+      <c r="I12" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="44" t="s">
+        <v>53</v>
+      </c>
       <c r="O12" s="44"/>
-      <c r="P12" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q12" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="R12" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S12" s="49">
+      <c r="P12" s="39"/>
+      <c r="Q12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="R12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="S12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="T12" s="44">
         <v>1</v>
       </c>
-      <c r="T12" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="U12" s="49">
+      <c r="U12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="V12" s="44">
         <v>2</v>
       </c>
-      <c r="V12" s="44"/>
-      <c r="W12" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="X12" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y12" s="44"/>
-      <c r="Z12" s="44"/>
-      <c r="AA12" s="44"/>
-      <c r="AB12" s="44"/>
+      <c r="W12" s="39"/>
+      <c r="X12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z12" s="39"/>
+      <c r="AA12" s="39"/>
+      <c r="AB12" s="39"/>
+      <c r="AC12" s="39"/>
     </row>
-    <row r="13" spans="1:28">
-      <c r="A13" s="44">
+    <row r="13" spans="1:29">
+      <c r="A13" s="39">
         <v>7</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="46">
+      <c r="D13" s="52" t="s">
+        <v>166</v>
+      </c>
+      <c r="E13" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="F13" s="41">
         <v>1</v>
       </c>
-      <c r="F13" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="J13" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="K13" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="L13" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="M13" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="N13" s="46"/>
-      <c r="O13" s="44"/>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="R13" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="S13" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="T13" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="U13" s="46">
+      <c r="G13" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="M13" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="O13" s="41"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="41"/>
+      <c r="R13" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="S13" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="T13" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="U13" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="V13" s="41">
         <v>2</v>
       </c>
-      <c r="V13" s="44"/>
-      <c r="W13" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="X13" s="46"/>
-      <c r="Y13" s="44"/>
-      <c r="Z13" s="44"/>
-      <c r="AA13" s="44"/>
-      <c r="AB13" s="44"/>
+      <c r="W13" s="39"/>
+      <c r="X13" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y13" s="41"/>
+      <c r="Z13" s="39"/>
+      <c r="AA13" s="39"/>
+      <c r="AB13" s="39"/>
+      <c r="AC13" s="39"/>
     </row>
-    <row r="14" spans="1:28">
-      <c r="A14" s="44">
+    <row r="14" spans="1:29">
+      <c r="A14" s="39">
         <v>8</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="43" t="s">
         <v>183</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="49">
+      <c r="D14" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="E14" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="F14" s="44">
         <v>1</v>
       </c>
-      <c r="F14" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="J14" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="K14" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="N14" s="49"/>
+      <c r="G14" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14" s="44"/>
+      <c r="N14" s="44" t="s">
+        <v>53</v>
+      </c>
       <c r="O14" s="44"/>
-      <c r="P14" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q14" s="49"/>
-      <c r="R14" s="49"/>
-      <c r="S14" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="T14" s="49"/>
-      <c r="U14" s="49"/>
+      <c r="P14" s="39"/>
+      <c r="Q14" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="U14" s="44"/>
       <c r="V14" s="44"/>
-      <c r="W14" s="49"/>
-      <c r="X14" s="49"/>
+      <c r="W14" s="39"/>
+      <c r="X14" s="44"/>
       <c r="Y14" s="44"/>
-      <c r="Z14" s="44"/>
-      <c r="AA14" s="44"/>
-      <c r="AB14" s="44"/>
+      <c r="Z14" s="39"/>
+      <c r="AA14" s="39"/>
+      <c r="AB14" s="39"/>
+      <c r="AC14" s="39"/>
     </row>
-    <row r="15" spans="1:28">
-      <c r="A15" s="44">
+    <row r="15" spans="1:29">
+      <c r="A15" s="39">
         <v>9</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="40" t="s">
         <v>205</v>
       </c>
-      <c r="C15" s="46" t="s">
+      <c r="C15" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="46">
+      <c r="D15" s="52" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="F15" s="41">
         <v>1</v>
       </c>
-      <c r="F15" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="I15" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="J15" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="K15" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="L15" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="M15" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="N15" s="46"/>
-      <c r="O15" s="44"/>
-      <c r="P15" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q15" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="R15" s="46">
+      <c r="G15" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="I15" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="M15" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="N15" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="O15" s="41"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="R15" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="S15" s="41">
         <v>1</v>
       </c>
-      <c r="S15" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="T15" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="U15" s="46">
+      <c r="T15" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="U15" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="V15" s="41">
         <v>2</v>
       </c>
-      <c r="V15" s="44"/>
-      <c r="W15" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="X15" s="46">
+      <c r="W15" s="39"/>
+      <c r="X15" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y15" s="41">
         <v>1</v>
       </c>
-      <c r="Y15" s="44"/>
-      <c r="Z15" s="44"/>
-      <c r="AA15" s="44"/>
-      <c r="AB15" s="44"/>
+      <c r="Z15" s="39"/>
+      <c r="AA15" s="39"/>
+      <c r="AB15" s="39"/>
+      <c r="AC15" s="39"/>
     </row>
-    <row r="16" spans="1:28">
-      <c r="A16" s="44">
+    <row r="16" spans="1:29">
+      <c r="A16" s="39">
         <v>10</v>
       </c>
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="43" t="s">
         <v>226</v>
       </c>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="44" t="s">
         <v>225</v>
       </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="49">
+      <c r="D16" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="E16" s="53" t="s">
+        <v>224</v>
+      </c>
+      <c r="F16" s="44">
         <v>1</v>
       </c>
-      <c r="F16" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="I16" s="49">
+      <c r="G16" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="J16" s="44">
         <v>2</v>
       </c>
-      <c r="J16" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="K16" s="49">
+      <c r="K16" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" s="44">
         <v>1</v>
       </c>
-      <c r="L16" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="M16" s="49">
+      <c r="M16" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="N16" s="44">
         <v>2</v>
       </c>
-      <c r="N16" s="49"/>
       <c r="O16" s="44"/>
-      <c r="P16" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q16" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="R16" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S16" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="T16" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="U16" s="49">
+      <c r="P16" s="39"/>
+      <c r="Q16" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="R16" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="S16" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="T16" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="U16" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="V16" s="44">
         <v>2</v>
       </c>
-      <c r="V16" s="44"/>
-      <c r="W16" s="49"/>
-      <c r="X16" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y16" s="44"/>
-      <c r="Z16" s="44"/>
-      <c r="AA16" s="44"/>
-      <c r="AB16" s="44"/>
+      <c r="W16" s="39"/>
+      <c r="X16" s="44"/>
+      <c r="Y16" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z16" s="39"/>
+      <c r="AA16" s="39"/>
+      <c r="AB16" s="39"/>
+      <c r="AC16" s="39"/>
     </row>
-    <row r="17" spans="1:28">
-      <c r="A17" s="44">
+    <row r="17" spans="1:29">
+      <c r="A17" s="39">
         <v>11</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="D17" s="44"/>
-      <c r="E17" s="46">
+      <c r="D17" s="52" t="s">
+        <v>239</v>
+      </c>
+      <c r="E17" s="52" t="s">
+        <v>240</v>
+      </c>
+      <c r="F17" s="41">
         <v>1</v>
       </c>
-      <c r="F17" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="H17" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="I17" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="J17" s="46">
+      <c r="G17" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="J17" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="K17" s="41">
         <v>1</v>
       </c>
-      <c r="K17" s="46">
+      <c r="L17" s="41">
         <v>1</v>
       </c>
-      <c r="L17" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="M17" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="N17" s="46"/>
-      <c r="O17" s="44"/>
-      <c r="P17" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q17" s="46"/>
-      <c r="R17" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="S17" s="46"/>
-      <c r="T17" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="U17" s="46">
+      <c r="M17" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="N17" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="O17" s="41"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="R17" s="41"/>
+      <c r="S17" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="V17" s="41">
         <v>2</v>
       </c>
-      <c r="V17" s="44"/>
-      <c r="W17" s="46"/>
-      <c r="X17" s="46"/>
-      <c r="Y17" s="44"/>
-      <c r="Z17" s="44"/>
-      <c r="AA17" s="44"/>
-      <c r="AB17" s="44"/>
+      <c r="W17" s="39"/>
+      <c r="X17" s="41"/>
+      <c r="Y17" s="41"/>
+      <c r="Z17" s="39"/>
+      <c r="AA17" s="39"/>
+      <c r="AB17" s="39"/>
+      <c r="AC17" s="39"/>
     </row>
-    <row r="18" spans="1:28">
-      <c r="A18" s="44">
+    <row r="18" spans="1:29">
+      <c r="A18" s="39">
         <v>12</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="43" t="s">
         <v>258</v>
       </c>
-      <c r="C18" s="49" t="s">
+      <c r="C18" s="44" t="s">
         <v>257</v>
       </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49">
+      <c r="D18" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44">
         <v>1</v>
       </c>
-      <c r="G18" s="49">
+      <c r="H18" s="44">
         <v>1</v>
       </c>
-      <c r="H18" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="I18" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="J18" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="K18" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="L18" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="M18" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="N18" s="49"/>
+      <c r="I18" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M18" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18" s="44" t="s">
+        <v>53</v>
+      </c>
       <c r="O18" s="44"/>
-      <c r="P18" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q18" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="R18" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S18" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="T18" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="U18" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="V18" s="44"/>
-      <c r="W18" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="X18" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y18" s="44"/>
-      <c r="Z18" s="44"/>
-      <c r="AA18" s="44"/>
-      <c r="AB18" s="44"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="R18" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="S18" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="T18" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="U18" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="V18" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="W18" s="39"/>
+      <c r="X18" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y18" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z18" s="39"/>
+      <c r="AA18" s="39"/>
+      <c r="AB18" s="39"/>
+      <c r="AC18" s="39"/>
     </row>
-    <row r="19" spans="1:28">
-      <c r="A19" s="44">
+    <row r="19" spans="1:29">
+      <c r="A19" s="39">
         <v>13</v>
       </c>
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="40" t="s">
         <v>282</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="41" t="s">
         <v>280</v>
       </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="46">
+      <c r="D19" s="52" t="s">
+        <v>278</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>279</v>
+      </c>
+      <c r="F19" s="41">
         <v>0.5</v>
       </c>
-      <c r="F19" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="I19" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46" t="s">
+      <c r="G19" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="J19" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41" t="s">
         <v>294</v>
       </c>
-      <c r="L19" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46"/>
-      <c r="O19" s="44"/>
-      <c r="P19" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q19" s="46"/>
-      <c r="R19" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="S19" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="T19" s="46"/>
-      <c r="U19" s="46"/>
-      <c r="V19" s="44"/>
-      <c r="W19" s="46"/>
-      <c r="X19" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y19" s="44"/>
-      <c r="Z19" s="44"/>
-      <c r="AA19" s="44"/>
-      <c r="AB19" s="44"/>
+      <c r="M19" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19" s="41"/>
+      <c r="O19" s="41"/>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="R19" s="41"/>
+      <c r="S19" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="T19" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="U19" s="41"/>
+      <c r="V19" s="41"/>
+      <c r="W19" s="39"/>
+      <c r="X19" s="41"/>
+      <c r="Y19" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z19" s="39"/>
+      <c r="AA19" s="39"/>
+      <c r="AB19" s="39"/>
+      <c r="AC19" s="39"/>
     </row>
-    <row r="20" spans="1:28">
-      <c r="A20" s="44">
+    <row r="20" spans="1:29">
+      <c r="A20" s="39">
         <v>14</v>
       </c>
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="43" t="s">
         <v>303</v>
       </c>
-      <c r="C20" s="49" t="s">
+      <c r="C20" s="44" t="s">
         <v>302</v>
       </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="H20" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="I20" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="J20" s="49">
+      <c r="D20" s="53" t="s">
+        <v>300</v>
+      </c>
+      <c r="E20" s="53" t="s">
+        <v>301</v>
+      </c>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="J20" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K20" s="44">
         <v>3</v>
       </c>
-      <c r="K20" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="L20" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="M20" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="N20" s="49"/>
+      <c r="L20" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M20" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="N20" s="44" t="s">
+        <v>53</v>
+      </c>
       <c r="O20" s="44"/>
-      <c r="P20" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q20" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="R20" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S20" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="T20" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="U20" s="49">
+      <c r="P20" s="39"/>
+      <c r="Q20" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="R20" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="S20" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="T20" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="U20" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="V20" s="44">
         <v>2</v>
       </c>
-      <c r="V20" s="44"/>
-      <c r="W20" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="X20" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y20" s="44"/>
-      <c r="Z20" s="44"/>
-      <c r="AA20" s="44"/>
-      <c r="AB20" s="44"/>
+      <c r="W20" s="39"/>
+      <c r="X20" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y20" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z20" s="39"/>
+      <c r="AA20" s="39"/>
+      <c r="AB20" s="39"/>
+      <c r="AC20" s="39"/>
     </row>
-    <row r="21" spans="1:28">
-      <c r="A21" s="44">
+    <row r="21" spans="1:29">
+      <c r="A21" s="39">
         <v>15</v>
       </c>
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="40" t="s">
         <v>321</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="41" t="s">
         <v>320</v>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="46">
+      <c r="D21" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>319</v>
+      </c>
+      <c r="F21" s="41">
         <v>1</v>
       </c>
-      <c r="F21" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="H21" s="50">
+      <c r="G21" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="I21" s="45">
         <v>1</v>
       </c>
-      <c r="I21" s="46">
+      <c r="J21" s="41">
         <v>1</v>
       </c>
-      <c r="J21" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="K21" s="46">
+      <c r="K21" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="L21" s="41">
         <v>3</v>
       </c>
-      <c r="L21" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
-      <c r="O21" s="44"/>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="S21" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="T21" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="U21" s="46">
+      <c r="M21" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="N21" s="41"/>
+      <c r="O21" s="41"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="41"/>
+      <c r="R21" s="41"/>
+      <c r="S21" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="T21" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="U21" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="V21" s="41">
         <v>2</v>
       </c>
-      <c r="V21" s="44"/>
-      <c r="W21" s="46"/>
-      <c r="X21" s="46"/>
-      <c r="Y21" s="44"/>
-      <c r="Z21" s="44"/>
-      <c r="AA21" s="44"/>
-      <c r="AB21" s="44"/>
+      <c r="W21" s="39"/>
+      <c r="X21" s="41"/>
+      <c r="Y21" s="41"/>
+      <c r="Z21" s="39"/>
+      <c r="AA21" s="39"/>
+      <c r="AB21" s="39"/>
+      <c r="AC21" s="39"/>
     </row>
-    <row r="22" spans="1:28">
-      <c r="A22" s="44">
+    <row r="22" spans="1:29">
+      <c r="A22" s="39">
         <v>16</v>
       </c>
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="43" t="s">
         <v>296</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="C22" s="44" t="s">
         <v>338</v>
       </c>
-      <c r="D22" s="44"/>
-      <c r="E22" s="49">
+      <c r="D22" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="F22" s="44">
         <v>1</v>
       </c>
-      <c r="F22" s="49">
+      <c r="G22" s="44">
         <v>1</v>
       </c>
-      <c r="G22" s="49">
+      <c r="H22" s="44">
         <v>1</v>
       </c>
-      <c r="H22" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="I22" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="J22" s="49">
+      <c r="I22" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K22" s="44">
         <v>1</v>
       </c>
-      <c r="K22" s="49">
+      <c r="L22" s="44">
         <v>2</v>
       </c>
-      <c r="L22" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="M22" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="N22" s="49"/>
+      <c r="M22" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="N22" s="44" t="s">
+        <v>53</v>
+      </c>
       <c r="O22" s="44"/>
-      <c r="P22" s="49">
+      <c r="P22" s="39"/>
+      <c r="Q22" s="44">
         <v>1</v>
       </c>
-      <c r="Q22" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="R22" s="49">
+      <c r="R22" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="S22" s="44">
         <v>1</v>
       </c>
-      <c r="S22" s="49">
+      <c r="T22" s="44">
         <v>2</v>
       </c>
-      <c r="T22" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="U22" s="49">
+      <c r="U22" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="V22" s="44">
         <v>2</v>
       </c>
-      <c r="V22" s="44"/>
-      <c r="W22" s="49">
+      <c r="W22" s="39"/>
+      <c r="X22" s="44">
         <v>1</v>
       </c>
-      <c r="X22" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y22" s="44"/>
-      <c r="Z22" s="44"/>
-      <c r="AA22" s="44"/>
-      <c r="AB22" s="44"/>
+      <c r="Y22" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z22" s="39"/>
+      <c r="AA22" s="39"/>
+      <c r="AB22" s="39"/>
+      <c r="AC22" s="39"/>
     </row>
-    <row r="23" spans="1:28">
-      <c r="A23" s="44">
+    <row r="23" spans="1:29">
+      <c r="A23" s="39">
         <v>17</v>
       </c>
-      <c r="B23" s="45" t="s">
+      <c r="B23" s="40" t="s">
         <v>352</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="46">
+      <c r="D23" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="E23" s="52" t="s">
+        <v>350</v>
+      </c>
+      <c r="F23" s="41">
         <v>1</v>
       </c>
-      <c r="F23" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="46">
+      <c r="G23" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="H23" s="41">
         <v>1</v>
       </c>
-      <c r="H23" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="I23" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="J23" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="K23" s="46">
+      <c r="I23" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="J23" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="K23" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="L23" s="41">
         <v>1</v>
       </c>
-      <c r="L23" s="46">
+      <c r="M23" s="41">
         <v>1</v>
       </c>
-      <c r="M23" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="N23" s="46"/>
-      <c r="O23" s="44"/>
-      <c r="P23" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q23" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="R23" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="S23" s="46">
+      <c r="N23" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="O23" s="41"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="R23" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="S23" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="T23" s="41">
         <v>1</v>
       </c>
-      <c r="T23" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="U23" s="46">
+      <c r="U23" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="V23" s="41">
         <v>2</v>
       </c>
-      <c r="V23" s="44"/>
-      <c r="W23" s="46">
+      <c r="W23" s="39"/>
+      <c r="X23" s="41">
         <v>1</v>
       </c>
-      <c r="X23" s="46">
+      <c r="Y23" s="41">
         <v>2</v>
       </c>
-      <c r="Y23" s="44"/>
-      <c r="Z23" s="44"/>
-      <c r="AA23" s="44"/>
-      <c r="AB23" s="44"/>
+      <c r="Z23" s="39"/>
+      <c r="AA23" s="39"/>
+      <c r="AB23" s="39"/>
+      <c r="AC23" s="39"/>
     </row>
-    <row r="24" spans="1:28">
-      <c r="A24" s="44">
+    <row r="24" spans="1:29">
+      <c r="A24" s="39">
         <v>18</v>
       </c>
-      <c r="B24" s="48" t="s">
+      <c r="B24" s="43" t="s">
         <v>365</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="44" t="s">
         <v>364</v>
       </c>
-      <c r="D24" s="44"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24" s="49">
+      <c r="D24" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H24" s="44">
         <v>2</v>
       </c>
-      <c r="H24" s="47"/>
-      <c r="I24" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="J24" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="K24" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="L24" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="M24" s="51">
+      <c r="I24" s="42"/>
+      <c r="J24" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K24" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="L24" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M24" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="N24" s="46">
         <v>2</v>
       </c>
-      <c r="N24" s="49"/>
       <c r="O24" s="44"/>
-      <c r="P24" s="49"/>
-      <c r="Q24" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="R24" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S24" s="49"/>
-      <c r="T24" s="49"/>
-      <c r="U24" s="49">
+      <c r="P24" s="39"/>
+      <c r="Q24" s="44"/>
+      <c r="R24" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="S24" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="T24" s="44"/>
+      <c r="U24" s="44"/>
+      <c r="V24" s="44">
         <v>2</v>
       </c>
-      <c r="V24" s="44"/>
-      <c r="W24" s="49"/>
-      <c r="X24" s="49">
+      <c r="W24" s="39"/>
+      <c r="X24" s="44"/>
+      <c r="Y24" s="44">
         <v>1</v>
       </c>
-      <c r="Y24" s="44"/>
-      <c r="Z24" s="44"/>
-      <c r="AA24" s="44"/>
-      <c r="AB24" s="44"/>
+      <c r="Z24" s="39"/>
+      <c r="AA24" s="39"/>
+      <c r="AB24" s="39"/>
+      <c r="AC24" s="39"/>
     </row>
-    <row r="25" spans="1:28">
-      <c r="A25" s="44">
+    <row r="25" spans="1:29">
+      <c r="A25" s="39">
         <v>19</v>
       </c>
-      <c r="B25" s="45" t="s">
+      <c r="B25" s="40" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="41" t="s">
         <v>374</v>
       </c>
-      <c r="D25" s="44"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="H25" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
-      <c r="O25" s="44"/>
-      <c r="P25" s="46"/>
-      <c r="Q25" s="46"/>
-      <c r="R25" s="46"/>
-      <c r="S25" s="46"/>
-      <c r="T25" s="46"/>
-      <c r="U25" s="46"/>
-      <c r="V25" s="44"/>
-      <c r="W25" s="46"/>
-      <c r="X25" s="46"/>
-      <c r="Y25" s="44"/>
-      <c r="Z25" s="44"/>
-      <c r="AA25" s="44"/>
-      <c r="AB25" s="44"/>
+      <c r="D25" s="52" t="s">
+        <v>372</v>
+      </c>
+      <c r="E25" s="52" t="s">
+        <v>373</v>
+      </c>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="I25" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="L25" s="41"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="41"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="41"/>
+      <c r="R25" s="41"/>
+      <c r="S25" s="41"/>
+      <c r="T25" s="41"/>
+      <c r="U25" s="41"/>
+      <c r="V25" s="41"/>
+      <c r="W25" s="39"/>
+      <c r="X25" s="41"/>
+      <c r="Y25" s="41"/>
+      <c r="Z25" s="39"/>
+      <c r="AA25" s="39"/>
+      <c r="AB25" s="39"/>
+      <c r="AC25" s="39"/>
     </row>
-    <row r="26" spans="1:28">
-      <c r="A26" s="44">
+    <row r="26" spans="1:29">
+      <c r="A26" s="39">
         <v>20</v>
       </c>
-      <c r="B26" s="48" t="s">
+      <c r="B26" s="43" t="s">
         <v>383</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C26" s="44" t="s">
         <v>382</v>
       </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="49">
+      <c r="D26" s="53" t="s">
+        <v>380</v>
+      </c>
+      <c r="E26" s="53" t="s">
+        <v>381</v>
+      </c>
+      <c r="F26" s="44">
         <v>1</v>
       </c>
-      <c r="F26" s="49">
+      <c r="G26" s="44">
         <v>1</v>
       </c>
-      <c r="G26" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="H26" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="I26" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="J26" s="49">
+      <c r="H26" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="J26" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K26" s="44">
         <v>2</v>
       </c>
-      <c r="K26" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="L26" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="M26" s="49"/>
-      <c r="N26" s="49"/>
+      <c r="L26" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M26" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="N26" s="44"/>
       <c r="O26" s="44"/>
-      <c r="P26" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q26" s="49"/>
-      <c r="R26" s="49"/>
-      <c r="S26" s="49"/>
-      <c r="T26" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="U26" s="49"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="R26" s="44"/>
+      <c r="S26" s="44"/>
+      <c r="T26" s="44"/>
+      <c r="U26" s="44" t="s">
+        <v>53</v>
+      </c>
       <c r="V26" s="44"/>
-      <c r="W26" s="49"/>
-      <c r="X26" s="49"/>
+      <c r="W26" s="39"/>
+      <c r="X26" s="44"/>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="44"/>
-      <c r="AA26" s="44"/>
-      <c r="AB26" s="44"/>
+      <c r="Z26" s="39"/>
+      <c r="AA26" s="39"/>
+      <c r="AB26" s="39"/>
+      <c r="AC26" s="39"/>
     </row>
-    <row r="27" spans="1:28">
-      <c r="A27" s="44">
+    <row r="27" spans="1:29">
+      <c r="A27" s="39">
         <v>21</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="40" t="s">
         <v>390</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="41" t="s">
         <v>389</v>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="46">
+      <c r="D27" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="F27" s="41">
         <v>1</v>
       </c>
-      <c r="F27" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="H27" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="I27" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="J27" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="K27" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="L27" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="M27" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="N27" s="46"/>
-      <c r="O27" s="44"/>
-      <c r="P27" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q27" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="R27" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="S27" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="T27" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="U27" s="46">
+      <c r="G27" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="I27" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="J27" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="K27" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="L27" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="M27" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="N27" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="O27" s="41"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="R27" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="S27" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="T27" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="U27" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="V27" s="41">
         <v>2</v>
       </c>
-      <c r="V27" s="44"/>
-      <c r="W27" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="X27" s="46">
+      <c r="W27" s="39"/>
+      <c r="X27" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y27" s="41">
         <v>1</v>
       </c>
-      <c r="Y27" s="44"/>
-      <c r="Z27" s="44"/>
-      <c r="AA27" s="44"/>
-      <c r="AB27" s="44"/>
+      <c r="Z27" s="39"/>
+      <c r="AA27" s="39"/>
+      <c r="AB27" s="39"/>
+      <c r="AC27" s="39"/>
     </row>
-    <row r="28" spans="1:28">
-      <c r="A28" s="44">
+    <row r="28" spans="1:29">
+      <c r="A28" s="39">
         <v>22</v>
       </c>
-      <c r="B28" s="48" t="s">
+      <c r="B28" s="43" t="s">
         <v>220</v>
       </c>
-      <c r="C28" s="49" t="s">
+      <c r="C28" s="44" t="s">
         <v>397</v>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="H28" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="I28" s="52">
+      <c r="D28" s="53" t="s">
+        <v>395</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>396</v>
+      </c>
+      <c r="F28" s="47"/>
+      <c r="G28" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="I28" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="J28" s="47">
         <v>1</v>
       </c>
-      <c r="J28" s="49">
+      <c r="K28" s="44">
         <v>1</v>
       </c>
-      <c r="K28" s="52"/>
-      <c r="L28" s="49">
+      <c r="L28" s="47"/>
+      <c r="M28" s="44">
         <v>1</v>
       </c>
-      <c r="M28" s="52"/>
-      <c r="N28" s="49"/>
+      <c r="N28" s="47"/>
       <c r="O28" s="44"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="52"/>
-      <c r="R28" s="49"/>
-      <c r="S28" s="52"/>
-      <c r="T28" s="49"/>
-      <c r="U28" s="52"/>
-      <c r="V28" s="44"/>
-      <c r="W28" s="52"/>
-      <c r="X28" s="49"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="47"/>
+      <c r="S28" s="44"/>
+      <c r="T28" s="47"/>
+      <c r="U28" s="44"/>
+      <c r="V28" s="47"/>
+      <c r="W28" s="39"/>
+      <c r="X28" s="47"/>
       <c r="Y28" s="44"/>
-      <c r="Z28" s="44"/>
-      <c r="AA28" s="44"/>
-      <c r="AB28" s="44"/>
+      <c r="Z28" s="39"/>
+      <c r="AA28" s="39"/>
+      <c r="AB28" s="39"/>
+      <c r="AC28" s="39"/>
     </row>
-    <row r="29" spans="1:28">
-      <c r="A29" s="44">
+    <row r="29" spans="1:29">
+      <c r="A29" s="39">
         <v>23</v>
       </c>
-      <c r="B29" s="45" t="s">
+      <c r="B29" s="40" t="s">
         <v>405</v>
       </c>
-      <c r="C29" s="46" t="s">
+      <c r="C29" s="41" t="s">
         <v>404</v>
       </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="46">
+      <c r="D29" s="52" t="s">
+        <v>402</v>
+      </c>
+      <c r="E29" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="F29" s="41">
         <v>1</v>
       </c>
-      <c r="F29" s="46">
+      <c r="G29" s="41">
         <v>1</v>
       </c>
-      <c r="G29" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="H29" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="I29" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="J29" s="46">
+      <c r="H29" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="I29" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="J29" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="K29" s="41">
         <v>1</v>
       </c>
-      <c r="K29" s="46">
+      <c r="L29" s="41">
         <v>1</v>
       </c>
-      <c r="L29" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="M29" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="N29" s="46"/>
-      <c r="O29" s="44"/>
-      <c r="P29" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q29" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="R29" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="S29" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="T29" s="46">
+      <c r="M29" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="N29" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="O29" s="41"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="R29" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="S29" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="T29" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="U29" s="41">
         <v>3</v>
       </c>
-      <c r="U29" s="46">
+      <c r="V29" s="41">
         <v>2</v>
       </c>
-      <c r="V29" s="44"/>
-      <c r="W29" s="46">
+      <c r="W29" s="39"/>
+      <c r="X29" s="41">
         <v>1</v>
       </c>
-      <c r="X29" s="46" t="s">
+      <c r="Y29" s="41" t="s">
         <v>408</v>
       </c>
-      <c r="Y29" s="44"/>
-      <c r="Z29" s="44"/>
-      <c r="AA29" s="44"/>
-      <c r="AB29" s="44"/>
+      <c r="Z29" s="39"/>
+      <c r="AA29" s="39"/>
+      <c r="AB29" s="39"/>
+      <c r="AC29" s="39"/>
     </row>
-    <row r="30" spans="1:28">
-      <c r="A30" s="44">
+    <row r="30" spans="1:29">
+      <c r="A30" s="39">
         <v>24</v>
       </c>
-      <c r="B30" s="48" t="s">
+      <c r="B30" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="49" t="s">
+      <c r="C30" s="44" t="s">
         <v>411</v>
       </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G30" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="H30" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="I30" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="J30" s="49"/>
-      <c r="K30" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="L30" s="49"/>
-      <c r="M30" s="49"/>
-      <c r="N30" s="49"/>
+      <c r="D30" s="53" t="s">
+        <v>409</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>410</v>
+      </c>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="J30" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K30" s="44"/>
+      <c r="L30" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M30" s="44"/>
+      <c r="N30" s="44"/>
       <c r="O30" s="44"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="49"/>
-      <c r="R30" s="49"/>
-      <c r="S30" s="49"/>
-      <c r="T30" s="49"/>
-      <c r="U30" s="49"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="44"/>
+      <c r="S30" s="44"/>
+      <c r="T30" s="44"/>
+      <c r="U30" s="44"/>
       <c r="V30" s="44"/>
-      <c r="W30" s="49"/>
-      <c r="X30" s="49"/>
+      <c r="W30" s="39"/>
+      <c r="X30" s="44"/>
       <c r="Y30" s="44"/>
-      <c r="Z30" s="44"/>
-      <c r="AA30" s="44"/>
-      <c r="AB30" s="44"/>
+      <c r="Z30" s="39"/>
+      <c r="AA30" s="39"/>
+      <c r="AB30" s="39"/>
+      <c r="AC30" s="39"/>
     </row>
-    <row r="31" spans="1:28">
-      <c r="A31" s="44">
+    <row r="31" spans="1:29">
+      <c r="A31" s="39">
         <v>25</v>
       </c>
-      <c r="B31" s="45" t="s">
+      <c r="B31" s="40" t="s">
         <v>418</v>
       </c>
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="41" t="s">
         <v>417</v>
       </c>
-      <c r="D31" s="44"/>
-      <c r="E31" s="46">
+      <c r="D31" s="52" t="s">
+        <v>415</v>
+      </c>
+      <c r="E31" s="52" t="s">
+        <v>416</v>
+      </c>
+      <c r="F31" s="41">
         <v>1</v>
       </c>
-      <c r="F31" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="G31" s="46" t="s">
+      <c r="G31" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="41" t="s">
         <v>408</v>
       </c>
-      <c r="H31" s="47">
+      <c r="I31" s="42">
         <v>1</v>
       </c>
-      <c r="I31" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46">
+      <c r="J31" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="41">
         <v>5</v>
       </c>
-      <c r="L31" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="M31" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="N31" s="46"/>
-      <c r="O31" s="44"/>
-      <c r="P31" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q31" s="53" t="s">
+      <c r="M31" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="N31" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="O31" s="41"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="R31" s="48" t="s">
         <v>294</v>
       </c>
-      <c r="R31" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="S31" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="T31" s="46">
+      <c r="S31" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="T31" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="U31" s="41">
         <v>2</v>
       </c>
-      <c r="U31" s="46">
+      <c r="V31" s="41">
         <v>2</v>
       </c>
-      <c r="V31" s="44"/>
-      <c r="W31" s="46"/>
-      <c r="X31" s="46"/>
-      <c r="Y31" s="44"/>
-      <c r="Z31" s="44"/>
-      <c r="AA31" s="44"/>
-      <c r="AB31" s="44"/>
+      <c r="W31" s="39"/>
+      <c r="X31" s="41"/>
+      <c r="Y31" s="41"/>
+      <c r="Z31" s="39"/>
+      <c r="AA31" s="39"/>
+      <c r="AB31" s="39"/>
+      <c r="AC31" s="39"/>
     </row>
-    <row r="32" spans="1:28">
-      <c r="A32" s="44">
+    <row r="32" spans="1:29">
+      <c r="A32" s="39">
         <v>26</v>
       </c>
-      <c r="B32" s="48" t="s">
+      <c r="B32" s="43" t="s">
         <v>425</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="C32" s="44" t="s">
         <v>424</v>
       </c>
-      <c r="D32" s="44"/>
-      <c r="E32" s="49">
+      <c r="D32" s="53" t="s">
+        <v>422</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>423</v>
+      </c>
+      <c r="F32" s="44">
         <v>1</v>
       </c>
-      <c r="F32" s="49">
+      <c r="G32" s="44">
         <v>2</v>
       </c>
-      <c r="G32" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="H32" s="50">
+      <c r="H32" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="I32" s="45">
         <v>1</v>
       </c>
-      <c r="I32" s="49">
+      <c r="J32" s="44">
         <v>1</v>
       </c>
-      <c r="J32" s="49">
+      <c r="K32" s="44">
         <v>2</v>
       </c>
-      <c r="K32" s="49">
+      <c r="L32" s="44">
         <v>2</v>
       </c>
-      <c r="L32" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="M32" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="N32" s="49"/>
+      <c r="M32" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="N32" s="44" t="s">
+        <v>53</v>
+      </c>
       <c r="O32" s="44"/>
-      <c r="P32" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q32" s="49">
+      <c r="P32" s="39"/>
+      <c r="Q32" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="R32" s="44">
         <v>2</v>
       </c>
-      <c r="R32" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S32" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="T32" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="U32" s="49">
+      <c r="S32" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="T32" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="U32" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="V32" s="44">
         <v>4</v>
       </c>
-      <c r="V32" s="44"/>
-      <c r="W32" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="X32" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y32" s="44"/>
-      <c r="Z32" s="44"/>
-      <c r="AA32" s="44"/>
-      <c r="AB32" s="44"/>
+      <c r="W32" s="39"/>
+      <c r="X32" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y32" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z32" s="39"/>
+      <c r="AA32" s="39"/>
+      <c r="AB32" s="39"/>
+      <c r="AC32" s="39"/>
     </row>
-    <row r="33" spans="1:28">
-      <c r="A33" s="44">
+    <row r="33" spans="1:29">
+      <c r="A33" s="39">
         <v>27</v>
       </c>
-      <c r="B33" s="45" t="s">
+      <c r="B33" s="40" t="s">
         <v>433</v>
       </c>
-      <c r="C33" s="46" t="s">
+      <c r="C33" s="41" t="s">
         <v>432</v>
       </c>
-      <c r="D33" s="44"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="H33" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="I33" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="J33" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="K33" s="46"/>
-      <c r="L33" s="46" t="s">
+      <c r="D33" s="52" t="s">
+        <v>430</v>
+      </c>
+      <c r="E33" s="52" t="s">
+        <v>431</v>
+      </c>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="I33" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="J33" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="K33" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41" t="s">
         <v>408</v>
       </c>
-      <c r="M33" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="N33" s="46"/>
-      <c r="O33" s="44"/>
-      <c r="P33" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q33" s="46"/>
-      <c r="R33" s="46">
+      <c r="N33" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="O33" s="41"/>
+      <c r="P33" s="39"/>
+      <c r="Q33" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="R33" s="41"/>
+      <c r="S33" s="41">
         <v>1</v>
       </c>
-      <c r="S33" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="T33" s="46"/>
-      <c r="U33" s="46">
+      <c r="T33" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="U33" s="41"/>
+      <c r="V33" s="41">
         <v>2</v>
       </c>
-      <c r="V33" s="44"/>
-      <c r="W33" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="X33" s="46" t="s">
+      <c r="W33" s="39"/>
+      <c r="X33" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y33" s="41" t="s">
         <v>408</v>
       </c>
-      <c r="Y33" s="44"/>
-      <c r="Z33" s="44"/>
-      <c r="AA33" s="44"/>
-      <c r="AB33" s="44"/>
+      <c r="Z33" s="39"/>
+      <c r="AA33" s="39"/>
+      <c r="AB33" s="39"/>
+      <c r="AC33" s="39"/>
     </row>
-    <row r="34" spans="1:28">
-      <c r="A34" s="44">
+    <row r="34" spans="1:29">
+      <c r="A34" s="39">
         <v>28</v>
       </c>
-      <c r="B34" s="48" t="s">
+      <c r="B34" s="43" t="s">
         <v>282</v>
       </c>
-      <c r="C34" s="49" t="s">
+      <c r="C34" s="44" t="s">
         <v>440</v>
       </c>
-      <c r="D34" s="44"/>
-      <c r="E34" s="49">
+      <c r="D34" s="53" t="s">
+        <v>438</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>439</v>
+      </c>
+      <c r="F34" s="44">
         <v>2</v>
       </c>
-      <c r="F34" s="49">
+      <c r="G34" s="44">
         <v>1</v>
       </c>
-      <c r="G34" s="49">
+      <c r="H34" s="44">
         <v>3</v>
       </c>
-      <c r="H34" s="49">
+      <c r="I34" s="44">
         <v>2</v>
       </c>
-      <c r="I34" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="J34" s="49">
+      <c r="J34" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K34" s="44">
         <v>3.5</v>
       </c>
-      <c r="K34" s="49" t="s">
+      <c r="L34" s="44" t="s">
         <v>408</v>
       </c>
-      <c r="L34" s="49">
+      <c r="M34" s="44">
         <v>3</v>
       </c>
-      <c r="M34" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="N34" s="49"/>
+      <c r="N34" s="44" t="s">
+        <v>53</v>
+      </c>
       <c r="O34" s="44"/>
-      <c r="P34" s="49">
+      <c r="P34" s="39"/>
+      <c r="Q34" s="44">
         <v>2</v>
       </c>
-      <c r="Q34" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="R34" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S34" s="49">
+      <c r="R34" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="S34" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="T34" s="44">
         <v>1</v>
       </c>
-      <c r="T34" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="U34" s="49">
+      <c r="U34" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="V34" s="44">
         <v>2</v>
       </c>
-      <c r="V34" s="44"/>
-      <c r="W34" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="X34" s="49" t="s">
+      <c r="W34" s="39"/>
+      <c r="X34" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y34" s="44" t="s">
         <v>408</v>
       </c>
-      <c r="Y34" s="44"/>
-      <c r="Z34" s="44"/>
-      <c r="AA34" s="44"/>
-      <c r="AB34" s="44"/>
+      <c r="Z34" s="39"/>
+      <c r="AA34" s="39"/>
+      <c r="AB34" s="39"/>
+      <c r="AC34" s="39"/>
     </row>
-    <row r="35" spans="1:28">
-      <c r="A35" s="44">
+    <row r="35" spans="1:29">
+      <c r="A35" s="39">
         <v>29</v>
       </c>
-      <c r="B35" s="45" t="s">
+      <c r="B35" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="C35" s="46" t="s">
+      <c r="C35" s="41" t="s">
         <v>446</v>
       </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="G35" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="H35" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="I35" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="J35" s="46" t="s">
+      <c r="D35" s="52" t="s">
+        <v>444</v>
+      </c>
+      <c r="E35" s="52" t="s">
+        <v>445</v>
+      </c>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="H35" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="I35" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="J35" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="K35" s="41" t="s">
         <v>408</v>
       </c>
-      <c r="K35" s="46">
+      <c r="L35" s="41">
         <v>1</v>
       </c>
-      <c r="L35" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="M35" s="46" t="s">
+      <c r="M35" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="N35" s="41" t="s">
         <v>408</v>
       </c>
-      <c r="N35" s="46"/>
-      <c r="O35" s="44"/>
-      <c r="P35" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q35" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="R35" s="46">
+      <c r="O35" s="41"/>
+      <c r="P35" s="39"/>
+      <c r="Q35" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="R35" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="S35" s="41">
         <v>2</v>
       </c>
-      <c r="S35" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="T35" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="U35" s="46">
+      <c r="T35" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="U35" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="V35" s="41">
         <v>2</v>
       </c>
-      <c r="V35" s="44"/>
-      <c r="W35" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="X35" s="46">
+      <c r="W35" s="39"/>
+      <c r="X35" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y35" s="41">
         <v>2</v>
       </c>
-      <c r="Y35" s="44"/>
-      <c r="Z35" s="44"/>
-      <c r="AA35" s="44"/>
-      <c r="AB35" s="44"/>
+      <c r="Z35" s="39"/>
+      <c r="AA35" s="39"/>
+      <c r="AB35" s="39"/>
+      <c r="AC35" s="39"/>
     </row>
-    <row r="36" spans="1:28">
-      <c r="A36" s="44">
+    <row r="36" spans="1:29">
+      <c r="A36" s="39">
         <v>30</v>
       </c>
-      <c r="B36" s="48" t="s">
+      <c r="B36" s="43" t="s">
         <v>453</v>
       </c>
-      <c r="C36" s="49" t="s">
+      <c r="C36" s="44" t="s">
         <v>452</v>
       </c>
-      <c r="D36" s="44"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G36" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="H36" s="54" t="s">
+      <c r="D36" s="53" t="s">
+        <v>450</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>451</v>
+      </c>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H36" s="44" t="s">
         <v>53</v>
       </c>
       <c r="I36" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="J36" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="K36" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="L36" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="M36" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="N36" s="49"/>
+      <c r="J36" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K36" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="L36" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M36" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="N36" s="44" t="s">
+        <v>53</v>
+      </c>
       <c r="O36" s="44"/>
-      <c r="P36" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q36" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="R36" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="S36" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="T36" s="49">
+      <c r="P36" s="39"/>
+      <c r="Q36" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="R36" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="S36" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="T36" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="U36" s="44">
         <v>3</v>
       </c>
-      <c r="U36" s="49">
+      <c r="V36" s="44">
         <v>2</v>
       </c>
-      <c r="V36" s="44"/>
-      <c r="W36" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="X36" s="49">
+      <c r="W36" s="39"/>
+      <c r="X36" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y36" s="44">
         <v>1</v>
       </c>
-      <c r="Y36" s="44"/>
-      <c r="Z36" s="44"/>
-      <c r="AA36" s="44"/>
-      <c r="AB36" s="44"/>
+      <c r="Z36" s="39"/>
+      <c r="AA36" s="39"/>
+      <c r="AB36" s="39"/>
+      <c r="AC36" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
+  <mergeCells count="17">
+    <mergeCell ref="AB5:AC5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/Datos Tesis Upstream/Algoritmos y Programacion/2526-3/Asistencia y participacion Algoritmos 2526-3.xlsx
+++ b/Datos Tesis Upstream/Algoritmos y Programacion/2526-3/Asistencia y participacion Algoritmos 2526-3.xlsx
@@ -17,6 +17,7 @@
     <sheet name="sec 3" sheetId="2" r:id="rId2"/>
     <sheet name="sec 6" sheetId="3" r:id="rId3"/>
     <sheet name="Estandar" sheetId="4" r:id="rId4"/>
+    <sheet name="Cronograma" sheetId="5" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -15773,64 +15774,70 @@
       <c r="A17" s="39">
         <v>11</v>
       </c>
-      <c r="B17" s="40" t="s">
-        <v>220</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" s="52" t="s">
-        <v>239</v>
-      </c>
-      <c r="E17" s="52" t="s">
-        <v>240</v>
-      </c>
-      <c r="F17" s="41">
+      <c r="B17" s="43" t="s">
+        <v>258</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>257</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44">
         <v>1</v>
       </c>
-      <c r="G17" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="H17" s="41" t="s">
-        <v>53</v>
+      <c r="H17" s="44">
+        <v>1</v>
       </c>
       <c r="I17" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="J17" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K17" s="41">
-        <v>1</v>
-      </c>
-      <c r="L17" s="41">
-        <v>1</v>
-      </c>
-      <c r="M17" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="N17" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="O17" s="41"/>
+      <c r="J17" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K17" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M17" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="N17" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="O17" s="44"/>
       <c r="P17" s="39"/>
-      <c r="Q17" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="R17" s="41"/>
-      <c r="S17" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="T17" s="41"/>
-      <c r="U17" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="V17" s="41">
-        <v>2</v>
+      <c r="Q17" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="R17" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="S17" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="T17" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="U17" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="V17" s="44" t="s">
+        <v>53</v>
       </c>
       <c r="W17" s="39"/>
-      <c r="X17" s="41"/>
-      <c r="Y17" s="41"/>
+      <c r="X17" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y17" s="44" t="s">
+        <v>53</v>
+      </c>
       <c r="Z17" s="39"/>
       <c r="AA17" s="39"/>
       <c r="AB17" s="39"/>
@@ -15840,70 +15847,64 @@
       <c r="A18" s="39">
         <v>12</v>
       </c>
-      <c r="B18" s="43" t="s">
-        <v>258</v>
-      </c>
-      <c r="C18" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44">
+      <c r="B18" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>239</v>
+      </c>
+      <c r="E18" s="52" t="s">
+        <v>240</v>
+      </c>
+      <c r="F18" s="41">
         <v>1</v>
       </c>
-      <c r="H18" s="44">
+      <c r="G18" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="I18" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" s="41">
         <v>1</v>
       </c>
-      <c r="I18" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="J18" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="K18" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="L18" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="M18" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="N18" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="O18" s="44"/>
+      <c r="L18" s="41">
+        <v>1</v>
+      </c>
+      <c r="M18" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="O18" s="41"/>
       <c r="P18" s="39"/>
-      <c r="Q18" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="R18" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="S18" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="T18" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="U18" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="V18" s="44" t="s">
-        <v>53</v>
+      <c r="Q18" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="R18" s="41"/>
+      <c r="S18" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="V18" s="41">
+        <v>2</v>
       </c>
       <c r="W18" s="39"/>
-      <c r="X18" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y18" s="44" t="s">
-        <v>53</v>
-      </c>
+      <c r="X18" s="41"/>
+      <c r="Y18" s="41"/>
       <c r="Z18" s="39"/>
       <c r="AA18" s="39"/>
       <c r="AB18" s="39"/>
@@ -16640,48 +16641,66 @@
       <c r="A30" s="39">
         <v>24</v>
       </c>
-      <c r="B30" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="D30" s="53" t="s">
-        <v>409</v>
-      </c>
-      <c r="E30" s="53" t="s">
-        <v>410</v>
-      </c>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="H30" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="I30" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="J30" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="K30" s="44"/>
-      <c r="L30" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="M30" s="44"/>
-      <c r="N30" s="44"/>
-      <c r="O30" s="44"/>
+      <c r="B30" s="40" t="s">
+        <v>418</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>417</v>
+      </c>
+      <c r="D30" s="52" t="s">
+        <v>415</v>
+      </c>
+      <c r="E30" s="52" t="s">
+        <v>416</v>
+      </c>
+      <c r="F30" s="41">
+        <v>1</v>
+      </c>
+      <c r="G30" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="41" t="s">
+        <v>408</v>
+      </c>
+      <c r="I30" s="42">
+        <v>1</v>
+      </c>
+      <c r="J30" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="41">
+        <v>5</v>
+      </c>
+      <c r="M30" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="N30" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="O30" s="41"/>
       <c r="P30" s="39"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="44"/>
-      <c r="S30" s="44"/>
-      <c r="T30" s="44"/>
-      <c r="U30" s="44"/>
-      <c r="V30" s="44"/>
+      <c r="Q30" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="R30" s="48" t="s">
+        <v>294</v>
+      </c>
+      <c r="S30" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="T30" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="U30" s="41">
+        <v>2</v>
+      </c>
+      <c r="V30" s="41">
+        <v>2</v>
+      </c>
       <c r="W30" s="39"/>
-      <c r="X30" s="44"/>
-      <c r="Y30" s="44"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="41"/>
       <c r="Z30" s="39"/>
       <c r="AA30" s="39"/>
       <c r="AB30" s="39"/>
@@ -16691,66 +16710,48 @@
       <c r="A31" s="39">
         <v>25</v>
       </c>
-      <c r="B31" s="40" t="s">
-        <v>418</v>
-      </c>
-      <c r="C31" s="41" t="s">
-        <v>417</v>
-      </c>
-      <c r="D31" s="52" t="s">
-        <v>415</v>
-      </c>
-      <c r="E31" s="52" t="s">
-        <v>416</v>
-      </c>
-      <c r="F31" s="41">
-        <v>1</v>
-      </c>
-      <c r="G31" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="H31" s="41" t="s">
-        <v>408</v>
-      </c>
-      <c r="I31" s="42">
-        <v>1</v>
-      </c>
-      <c r="J31" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K31" s="41"/>
-      <c r="L31" s="41">
-        <v>5</v>
-      </c>
-      <c r="M31" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="N31" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="O31" s="41"/>
+      <c r="B31" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>411</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>409</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>410</v>
+      </c>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="J31" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K31" s="44"/>
+      <c r="L31" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M31" s="44"/>
+      <c r="N31" s="44"/>
+      <c r="O31" s="44"/>
       <c r="P31" s="39"/>
-      <c r="Q31" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="R31" s="48" t="s">
-        <v>294</v>
-      </c>
-      <c r="S31" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="T31" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="U31" s="41">
-        <v>2</v>
-      </c>
-      <c r="V31" s="41">
-        <v>2</v>
-      </c>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="44"/>
+      <c r="S31" s="44"/>
+      <c r="T31" s="44"/>
+      <c r="U31" s="44"/>
+      <c r="V31" s="44"/>
       <c r="W31" s="39"/>
-      <c r="X31" s="41"/>
-      <c r="Y31" s="41"/>
+      <c r="X31" s="44"/>
+      <c r="Y31" s="44"/>
       <c r="Z31" s="39"/>
       <c r="AA31" s="39"/>
       <c r="AB31" s="39"/>
@@ -17140,4 +17141,360 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semana</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dia_sesion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_sesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repaso</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repaso</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin_clase</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">administrativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema = código del catálogo de la asignatura. Si la sesión no cubre contenido nuevo: tema = 0 y tipo_sesion indica la causa (evaluacion, repaso, sin_clase, administrativa). Si tema &gt; 0 la sesión es de contenido y tipo_sesion queda vacío.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>